--- a/Demo/ng_oncho_9999_4_b_lab.xlsx
+++ b/Demo/ng_oncho_9999_4_b_lab.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5778D1BD-9890-4733-848F-451A81782E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4993BBCF-B1D4-4FD6-A197-233474551520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="136">
   <si>
     <t>type</t>
   </si>
@@ -441,13 +441,16 @@
   <si>
     <t>Total Number of Positive Pools: **${positive_count}**
 Total Number of Negative Pools: **${negative_count}**</t>
+  </si>
+  <si>
+    <t>PCR and qPCR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -522,6 +525,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -637,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -724,6 +733,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1661,7 +1671,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="10" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>66</v>
       </c>
@@ -2007,7 +2017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.125" customWidth="1"/>
@@ -2114,42 +2124,42 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B14" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C14" s="23" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-    </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>111</v>
-      </c>
+      <c r="A15" s="17"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2157,10 +2167,10 @@
         <v>81</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2168,10 +2178,10 @@
         <v>81</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2179,9 +2189,20 @@
         <v>81</v>
       </c>
       <c r="B19" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C20" s="16" t="s">
         <v>115</v>
       </c>
     </row>
